--- a/data/monthly/【2026年7月】月次数値.xlsx
+++ b/data/monthly/【2026年7月】月次数値.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="576" yWindow="4332" windowWidth="21792" windowHeight="10812"/>
+    <workbookView xWindow="312" yWindow="3924" windowWidth="21792" windowHeight="10812"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1376" uniqueCount="261">
   <si>
     <t>レポート開始日</t>
   </si>
@@ -664,6 +664,144 @@
   </si>
   <si>
     <t>2027-07-22</t>
+  </si>
+  <si>
+    <t>2026-07-09</t>
+  </si>
+  <si>
+    <t>PML　広尾店</t>
+  </si>
+  <si>
+    <t>2026-09-11</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>堀田歯科（リンク先変更前）</t>
+  </si>
+  <si>
+    <t>きしかわデンタルオフィス</t>
+  </si>
+  <si>
+    <t>2027-05-01</t>
+  </si>
+  <si>
+    <t>大神宮デンタルクリニック（2年目）</t>
+  </si>
+  <si>
+    <t>金町駅前ジャスミン歯科（2回目）</t>
+  </si>
+  <si>
+    <t>掛川整体院サウレ</t>
+  </si>
+  <si>
+    <t>鍼灸サロンNOA</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>DesignBody 御徒町店</t>
+  </si>
+  <si>
+    <t>有限会社 ムネケン</t>
+  </si>
+  <si>
+    <t>Healing Salon Ange</t>
+  </si>
+  <si>
+    <t>2026-11-27</t>
+  </si>
+  <si>
+    <t>アキュラデンタルクリニック</t>
+  </si>
+  <si>
+    <t>Beauty Salon Arona</t>
+  </si>
+  <si>
+    <t>堀田歯科</t>
+  </si>
+  <si>
+    <t>UESUGI美容鍼灸整骨院</t>
+  </si>
+  <si>
+    <t>2026-11-03</t>
+  </si>
+  <si>
+    <t>スカイハイ英語塾</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>すがや歯科クリニック</t>
+  </si>
+  <si>
+    <t>2026-09-28</t>
+  </si>
+  <si>
+    <t>むぎ歯科</t>
+  </si>
+  <si>
+    <t>2026-09-26</t>
+  </si>
+  <si>
+    <t>はま歯科医院</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>整体処 たくみ堂</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>千歳烏山ケンズ歯科</t>
+  </si>
+  <si>
+    <t>2026-08-03</t>
+  </si>
+  <si>
+    <t>GAJUM photo studio</t>
+  </si>
+  <si>
+    <t>ストレッチ&amp;ボディケア m.o.v.e巣鴨店</t>
+  </si>
+  <si>
+    <t>2026-07-27</t>
+  </si>
+  <si>
+    <t>COCORO エステサロン</t>
+  </si>
+  <si>
+    <t>2026-07-21</t>
+  </si>
+  <si>
+    <t>なかはら歯科クリニック</t>
+  </si>
+  <si>
+    <t>割田歯科医院</t>
+  </si>
+  <si>
+    <t>住友歯科医院</t>
+  </si>
+  <si>
+    <t>2026-07-16</t>
+  </si>
+  <si>
+    <t>はんだ歯科医院</t>
+  </si>
+  <si>
+    <t>竹内歯科クリニック（審美歯科）</t>
+  </si>
+  <si>
+    <t>2026-07-17</t>
+  </si>
+  <si>
+    <t>銀座トレーニングラボ</t>
   </si>
 </sst>
 </file>
@@ -681,6 +819,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1013,7 +1152,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Y141"/>
+  <dimension ref="A1:Y172"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
@@ -11163,6 +11302,2189 @@
       </c>
       <c r="Y141">
         <v>174.33333300000001</v>
+      </c>
+    </row>
+    <row r="142" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A142" t="s">
+        <v>25</v>
+      </c>
+      <c r="B142" t="s">
+        <v>26</v>
+      </c>
+      <c r="C142" t="s">
+        <v>260</v>
+      </c>
+      <c r="D142" t="s">
+        <v>226</v>
+      </c>
+      <c r="E142" t="s">
+        <v>29</v>
+      </c>
+      <c r="F142">
+        <v>9</v>
+      </c>
+      <c r="G142" t="s">
+        <v>30</v>
+      </c>
+      <c r="H142">
+        <v>352</v>
+      </c>
+      <c r="I142">
+        <v>1.213068</v>
+      </c>
+      <c r="J142">
+        <v>83.444444439999998</v>
+      </c>
+      <c r="K142" t="s">
+        <v>42</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>751</v>
+      </c>
+      <c r="N142" t="s">
+        <v>198</v>
+      </c>
+      <c r="O142">
+        <v>427</v>
+      </c>
+      <c r="P142">
+        <v>1758.782201</v>
+      </c>
+      <c r="Q142">
+        <v>9</v>
+      </c>
+      <c r="S142">
+        <v>83.444444000000004</v>
+      </c>
+      <c r="T142">
+        <v>2.1077279999999998</v>
+      </c>
+      <c r="U142">
+        <v>9</v>
+      </c>
+      <c r="V142">
+        <v>2.1077279999999998</v>
+      </c>
+      <c r="W142">
+        <v>83.444444000000004</v>
+      </c>
+      <c r="X142">
+        <v>3</v>
+      </c>
+      <c r="Y142">
+        <v>250.33333300000001</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A143" t="s">
+        <v>25</v>
+      </c>
+      <c r="B143" t="s">
+        <v>26</v>
+      </c>
+      <c r="C143" t="s">
+        <v>197</v>
+      </c>
+      <c r="D143" t="s">
+        <v>226</v>
+      </c>
+      <c r="E143" t="s">
+        <v>29</v>
+      </c>
+      <c r="F143">
+        <v>4</v>
+      </c>
+      <c r="G143" t="s">
+        <v>30</v>
+      </c>
+      <c r="H143">
+        <v>371</v>
+      </c>
+      <c r="I143">
+        <v>1.008086</v>
+      </c>
+      <c r="J143">
+        <v>113.5</v>
+      </c>
+      <c r="K143" t="s">
+        <v>42</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>454</v>
+      </c>
+      <c r="N143" t="s">
+        <v>259</v>
+      </c>
+      <c r="O143">
+        <v>374</v>
+      </c>
+      <c r="P143">
+        <v>1213.9037430000001</v>
+      </c>
+      <c r="Q143">
+        <v>4</v>
+      </c>
+      <c r="S143">
+        <v>113.5</v>
+      </c>
+      <c r="T143">
+        <v>1.0695190000000001</v>
+      </c>
+      <c r="U143">
+        <v>4</v>
+      </c>
+      <c r="V143">
+        <v>1.0695190000000001</v>
+      </c>
+      <c r="W143">
+        <v>113.5</v>
+      </c>
+      <c r="X143">
+        <v>2</v>
+      </c>
+      <c r="Y143">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="144" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A144" t="s">
+        <v>25</v>
+      </c>
+      <c r="B144" t="s">
+        <v>26</v>
+      </c>
+      <c r="C144" t="s">
+        <v>258</v>
+      </c>
+      <c r="D144" t="s">
+        <v>226</v>
+      </c>
+      <c r="E144" t="s">
+        <v>29</v>
+      </c>
+      <c r="F144">
+        <v>4</v>
+      </c>
+      <c r="G144" t="s">
+        <v>30</v>
+      </c>
+      <c r="H144">
+        <v>354</v>
+      </c>
+      <c r="I144">
+        <v>1.0254239999999999</v>
+      </c>
+      <c r="J144">
+        <v>101.75</v>
+      </c>
+      <c r="K144" t="s">
+        <v>42</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>407</v>
+      </c>
+      <c r="N144" t="s">
+        <v>256</v>
+      </c>
+      <c r="O144">
+        <v>363</v>
+      </c>
+      <c r="P144">
+        <v>1121.212121</v>
+      </c>
+      <c r="Q144">
+        <v>4</v>
+      </c>
+      <c r="S144">
+        <v>101.75</v>
+      </c>
+      <c r="T144">
+        <v>1.101928</v>
+      </c>
+      <c r="U144">
+        <v>6</v>
+      </c>
+      <c r="V144">
+        <v>1.6528929999999999</v>
+      </c>
+      <c r="W144">
+        <v>67.833332999999996</v>
+      </c>
+      <c r="X144">
+        <v>2</v>
+      </c>
+      <c r="Y144">
+        <v>203.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A145" t="s">
+        <v>25</v>
+      </c>
+      <c r="B145" t="s">
+        <v>26</v>
+      </c>
+      <c r="C145" t="s">
+        <v>257</v>
+      </c>
+      <c r="D145" t="s">
+        <v>226</v>
+      </c>
+      <c r="E145" t="s">
+        <v>29</v>
+      </c>
+      <c r="F145">
+        <v>10</v>
+      </c>
+      <c r="G145" t="s">
+        <v>30</v>
+      </c>
+      <c r="H145">
+        <v>324</v>
+      </c>
+      <c r="I145">
+        <v>1.0154319999999999</v>
+      </c>
+      <c r="J145">
+        <v>48.7</v>
+      </c>
+      <c r="K145" t="s">
+        <v>42</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>487</v>
+      </c>
+      <c r="N145" t="s">
+        <v>256</v>
+      </c>
+      <c r="O145">
+        <v>329</v>
+      </c>
+      <c r="P145">
+        <v>1480.2431610000001</v>
+      </c>
+      <c r="Q145">
+        <v>10</v>
+      </c>
+      <c r="S145">
+        <v>48.7</v>
+      </c>
+      <c r="T145">
+        <v>3.039514</v>
+      </c>
+      <c r="U145">
+        <v>11</v>
+      </c>
+      <c r="V145">
+        <v>3.3434650000000001</v>
+      </c>
+      <c r="W145">
+        <v>44.272727000000003</v>
+      </c>
+      <c r="X145">
+        <v>7</v>
+      </c>
+      <c r="Y145">
+        <v>69.571428999999995</v>
+      </c>
+    </row>
+    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A146" t="s">
+        <v>25</v>
+      </c>
+      <c r="B146" t="s">
+        <v>26</v>
+      </c>
+      <c r="C146" t="s">
+        <v>255</v>
+      </c>
+      <c r="D146" t="s">
+        <v>226</v>
+      </c>
+      <c r="E146" t="s">
+        <v>29</v>
+      </c>
+      <c r="F146">
+        <v>26</v>
+      </c>
+      <c r="G146" t="s">
+        <v>30</v>
+      </c>
+      <c r="H146">
+        <v>931</v>
+      </c>
+      <c r="I146">
+        <v>1.093448</v>
+      </c>
+      <c r="J146">
+        <v>34.5</v>
+      </c>
+      <c r="K146" t="s">
+        <v>42</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>897</v>
+      </c>
+      <c r="N146" t="s">
+        <v>252</v>
+      </c>
+      <c r="O146">
+        <v>1018</v>
+      </c>
+      <c r="P146">
+        <v>881.13948900000003</v>
+      </c>
+      <c r="Q146">
+        <v>26</v>
+      </c>
+      <c r="S146">
+        <v>34.5</v>
+      </c>
+      <c r="T146">
+        <v>2.5540280000000002</v>
+      </c>
+      <c r="U146">
+        <v>31</v>
+      </c>
+      <c r="V146">
+        <v>3.0451869999999999</v>
+      </c>
+      <c r="W146">
+        <v>28.935483999999999</v>
+      </c>
+      <c r="X146">
+        <v>20</v>
+      </c>
+      <c r="Y146">
+        <v>44.85</v>
+      </c>
+    </row>
+    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A147" t="s">
+        <v>25</v>
+      </c>
+      <c r="B147" t="s">
+        <v>26</v>
+      </c>
+      <c r="C147" t="s">
+        <v>254</v>
+      </c>
+      <c r="D147" t="s">
+        <v>226</v>
+      </c>
+      <c r="E147" t="s">
+        <v>29</v>
+      </c>
+      <c r="F147">
+        <v>24</v>
+      </c>
+      <c r="G147" t="s">
+        <v>30</v>
+      </c>
+      <c r="H147">
+        <v>710</v>
+      </c>
+      <c r="I147">
+        <v>1.08169</v>
+      </c>
+      <c r="J147">
+        <v>37.25</v>
+      </c>
+      <c r="K147" t="s">
+        <v>42</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>894</v>
+      </c>
+      <c r="N147" t="s">
+        <v>252</v>
+      </c>
+      <c r="O147">
+        <v>768</v>
+      </c>
+      <c r="P147">
+        <v>1164.0625</v>
+      </c>
+      <c r="Q147">
+        <v>24</v>
+      </c>
+      <c r="S147">
+        <v>37.25</v>
+      </c>
+      <c r="T147">
+        <v>3.125</v>
+      </c>
+      <c r="U147">
+        <v>27</v>
+      </c>
+      <c r="V147">
+        <v>3.515625</v>
+      </c>
+      <c r="W147">
+        <v>33.111111000000001</v>
+      </c>
+      <c r="X147">
+        <v>21</v>
+      </c>
+      <c r="Y147">
+        <v>42.571429000000002</v>
+      </c>
+    </row>
+    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B148" t="s">
+        <v>26</v>
+      </c>
+      <c r="C148" t="s">
+        <v>253</v>
+      </c>
+      <c r="D148" t="s">
+        <v>226</v>
+      </c>
+      <c r="E148" t="s">
+        <v>29</v>
+      </c>
+      <c r="F148">
+        <v>23</v>
+      </c>
+      <c r="G148" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148">
+        <v>373</v>
+      </c>
+      <c r="I148">
+        <v>1.02681</v>
+      </c>
+      <c r="J148">
+        <v>28.739130429999999</v>
+      </c>
+      <c r="K148" t="s">
+        <v>42</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>661</v>
+      </c>
+      <c r="N148" t="s">
+        <v>252</v>
+      </c>
+      <c r="O148">
+        <v>383</v>
+      </c>
+      <c r="P148">
+        <v>1725.8485639999999</v>
+      </c>
+      <c r="Q148">
+        <v>23</v>
+      </c>
+      <c r="S148">
+        <v>28.739129999999999</v>
+      </c>
+      <c r="T148">
+        <v>6.0052219999999998</v>
+      </c>
+      <c r="U148">
+        <v>23</v>
+      </c>
+      <c r="V148">
+        <v>6.0052219999999998</v>
+      </c>
+      <c r="W148">
+        <v>28.739129999999999</v>
+      </c>
+      <c r="X148">
+        <v>14</v>
+      </c>
+      <c r="Y148">
+        <v>47.214286000000001</v>
+      </c>
+    </row>
+    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>25</v>
+      </c>
+      <c r="B149" t="s">
+        <v>26</v>
+      </c>
+      <c r="C149" t="s">
+        <v>251</v>
+      </c>
+      <c r="D149" t="s">
+        <v>226</v>
+      </c>
+      <c r="E149" t="s">
+        <v>29</v>
+      </c>
+      <c r="F149">
+        <v>23</v>
+      </c>
+      <c r="G149" t="s">
+        <v>30</v>
+      </c>
+      <c r="H149">
+        <v>844</v>
+      </c>
+      <c r="I149">
+        <v>1.0722750000000001</v>
+      </c>
+      <c r="J149">
+        <v>34.086956520000001</v>
+      </c>
+      <c r="K149" t="s">
+        <v>42</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+      <c r="M149">
+        <v>784</v>
+      </c>
+      <c r="N149" t="s">
+        <v>250</v>
+      </c>
+      <c r="O149">
+        <v>905</v>
+      </c>
+      <c r="P149">
+        <v>866.29834300000005</v>
+      </c>
+      <c r="Q149">
+        <v>23</v>
+      </c>
+      <c r="S149">
+        <v>34.086956999999998</v>
+      </c>
+      <c r="T149">
+        <v>2.541436</v>
+      </c>
+      <c r="U149">
+        <v>23</v>
+      </c>
+      <c r="V149">
+        <v>2.541436</v>
+      </c>
+      <c r="W149">
+        <v>34.086956999999998</v>
+      </c>
+      <c r="X149">
+        <v>20</v>
+      </c>
+      <c r="Y149">
+        <v>39.200000000000003</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
+        <v>25</v>
+      </c>
+      <c r="B150" t="s">
+        <v>26</v>
+      </c>
+      <c r="C150" t="s">
+        <v>249</v>
+      </c>
+      <c r="D150" t="s">
+        <v>226</v>
+      </c>
+      <c r="E150" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150">
+        <v>32</v>
+      </c>
+      <c r="G150" t="s">
+        <v>30</v>
+      </c>
+      <c r="H150">
+        <v>1074</v>
+      </c>
+      <c r="I150">
+        <v>1.0735570000000001</v>
+      </c>
+      <c r="J150">
+        <v>46.375</v>
+      </c>
+      <c r="K150" t="s">
+        <v>42</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+      <c r="M150">
+        <v>1484</v>
+      </c>
+      <c r="N150" t="s">
+        <v>247</v>
+      </c>
+      <c r="O150">
+        <v>1153</v>
+      </c>
+      <c r="P150">
+        <v>1287.07719</v>
+      </c>
+      <c r="Q150">
+        <v>32</v>
+      </c>
+      <c r="S150">
+        <v>46.375</v>
+      </c>
+      <c r="T150">
+        <v>2.775369</v>
+      </c>
+      <c r="U150">
+        <v>37</v>
+      </c>
+      <c r="V150">
+        <v>3.2090200000000002</v>
+      </c>
+      <c r="W150">
+        <v>40.108108000000001</v>
+      </c>
+      <c r="X150">
+        <v>27</v>
+      </c>
+      <c r="Y150">
+        <v>54.962963000000002</v>
+      </c>
+    </row>
+    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A151" t="s">
+        <v>25</v>
+      </c>
+      <c r="B151" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" t="s">
+        <v>248</v>
+      </c>
+      <c r="D151" t="s">
+        <v>226</v>
+      </c>
+      <c r="E151" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151">
+        <v>49</v>
+      </c>
+      <c r="G151" t="s">
+        <v>30</v>
+      </c>
+      <c r="H151">
+        <v>2011</v>
+      </c>
+      <c r="I151">
+        <v>1.082049</v>
+      </c>
+      <c r="J151">
+        <v>45.897959180000001</v>
+      </c>
+      <c r="K151" t="s">
+        <v>42</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>2249</v>
+      </c>
+      <c r="N151" t="s">
+        <v>247</v>
+      </c>
+      <c r="O151">
+        <v>2176</v>
+      </c>
+      <c r="P151">
+        <v>1033.5477940000001</v>
+      </c>
+      <c r="Q151">
+        <v>49</v>
+      </c>
+      <c r="S151">
+        <v>45.897959</v>
+      </c>
+      <c r="T151">
+        <v>2.2518379999999998</v>
+      </c>
+      <c r="U151">
+        <v>50</v>
+      </c>
+      <c r="V151">
+        <v>2.2977940000000001</v>
+      </c>
+      <c r="W151">
+        <v>44.98</v>
+      </c>
+      <c r="X151">
+        <v>37</v>
+      </c>
+      <c r="Y151">
+        <v>60.783783999999997</v>
+      </c>
+    </row>
+    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A152" t="s">
+        <v>25</v>
+      </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" t="s">
+        <v>246</v>
+      </c>
+      <c r="D152" t="s">
+        <v>226</v>
+      </c>
+      <c r="E152" t="s">
+        <v>29</v>
+      </c>
+      <c r="F152">
+        <v>36</v>
+      </c>
+      <c r="G152" t="s">
+        <v>30</v>
+      </c>
+      <c r="H152">
+        <v>1784</v>
+      </c>
+      <c r="I152">
+        <v>1.0700670000000001</v>
+      </c>
+      <c r="J152">
+        <v>58.861111110000003</v>
+      </c>
+      <c r="K152" t="s">
+        <v>42</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+      <c r="M152">
+        <v>2119</v>
+      </c>
+      <c r="N152" t="s">
+        <v>245</v>
+      </c>
+      <c r="O152">
+        <v>1909</v>
+      </c>
+      <c r="P152">
+        <v>1110.005238</v>
+      </c>
+      <c r="Q152">
+        <v>36</v>
+      </c>
+      <c r="S152">
+        <v>58.861111000000001</v>
+      </c>
+      <c r="T152">
+        <v>1.885804</v>
+      </c>
+      <c r="U152">
+        <v>39</v>
+      </c>
+      <c r="V152">
+        <v>2.0429539999999999</v>
+      </c>
+      <c r="W152">
+        <v>54.333333000000003</v>
+      </c>
+      <c r="X152">
+        <v>23</v>
+      </c>
+      <c r="Y152">
+        <v>92.130435000000006</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A153" t="s">
+        <v>25</v>
+      </c>
+      <c r="B153" t="s">
+        <v>26</v>
+      </c>
+      <c r="C153" t="s">
+        <v>244</v>
+      </c>
+      <c r="D153" t="s">
+        <v>28</v>
+      </c>
+      <c r="E153" t="s">
+        <v>29</v>
+      </c>
+      <c r="F153">
+        <v>65</v>
+      </c>
+      <c r="G153" t="s">
+        <v>30</v>
+      </c>
+      <c r="H153">
+        <v>1114</v>
+      </c>
+      <c r="I153">
+        <v>1.1346499999999999</v>
+      </c>
+      <c r="J153">
+        <v>40.276923080000003</v>
+      </c>
+      <c r="K153" t="s">
+        <v>42</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>2618</v>
+      </c>
+      <c r="N153" t="s">
+        <v>243</v>
+      </c>
+      <c r="O153">
+        <v>1264</v>
+      </c>
+      <c r="P153">
+        <v>2071.2025319999998</v>
+      </c>
+      <c r="Q153">
+        <v>65</v>
+      </c>
+      <c r="S153">
+        <v>40.276922999999996</v>
+      </c>
+      <c r="T153">
+        <v>5.1424050000000001</v>
+      </c>
+      <c r="U153">
+        <v>68</v>
+      </c>
+      <c r="V153">
+        <v>5.3797470000000001</v>
+      </c>
+      <c r="W153">
+        <v>38.5</v>
+      </c>
+      <c r="X153">
+        <v>1</v>
+      </c>
+      <c r="Y153">
+        <v>2618</v>
+      </c>
+    </row>
+    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A154" t="s">
+        <v>25</v>
+      </c>
+      <c r="B154" t="s">
+        <v>26</v>
+      </c>
+      <c r="C154" t="s">
+        <v>242</v>
+      </c>
+      <c r="D154" t="s">
+        <v>28</v>
+      </c>
+      <c r="E154" t="s">
+        <v>29</v>
+      </c>
+      <c r="F154">
+        <v>62</v>
+      </c>
+      <c r="G154" t="s">
+        <v>30</v>
+      </c>
+      <c r="H154">
+        <v>3113</v>
+      </c>
+      <c r="I154">
+        <v>1.2306459999999999</v>
+      </c>
+      <c r="J154">
+        <v>55.677419350000001</v>
+      </c>
+      <c r="K154" t="s">
+        <v>42</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>3452</v>
+      </c>
+      <c r="N154" t="s">
+        <v>241</v>
+      </c>
+      <c r="O154">
+        <v>3831</v>
+      </c>
+      <c r="P154">
+        <v>901.07021699999996</v>
+      </c>
+      <c r="Q154">
+        <v>62</v>
+      </c>
+      <c r="S154">
+        <v>55.677419</v>
+      </c>
+      <c r="T154">
+        <v>1.618376</v>
+      </c>
+      <c r="U154">
+        <v>64</v>
+      </c>
+      <c r="V154">
+        <v>1.670582</v>
+      </c>
+      <c r="W154">
+        <v>53.9375</v>
+      </c>
+      <c r="X154">
+        <v>28</v>
+      </c>
+      <c r="Y154">
+        <v>123.285714</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>25</v>
+      </c>
+      <c r="B155" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" t="s">
+        <v>240</v>
+      </c>
+      <c r="D155" t="s">
+        <v>28</v>
+      </c>
+      <c r="E155" t="s">
+        <v>29</v>
+      </c>
+      <c r="F155">
+        <v>155</v>
+      </c>
+      <c r="G155" t="s">
+        <v>30</v>
+      </c>
+      <c r="H155">
+        <v>3968</v>
+      </c>
+      <c r="I155">
+        <v>1.2404230000000001</v>
+      </c>
+      <c r="J155">
+        <v>25.135483870000002</v>
+      </c>
+      <c r="K155" t="s">
+        <v>42</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>3896</v>
+      </c>
+      <c r="N155" t="s">
+        <v>239</v>
+      </c>
+      <c r="O155">
+        <v>4922</v>
+      </c>
+      <c r="P155">
+        <v>791.54815099999996</v>
+      </c>
+      <c r="Q155">
+        <v>155</v>
+      </c>
+      <c r="S155">
+        <v>25.135484000000002</v>
+      </c>
+      <c r="T155">
+        <v>3.1491259999999999</v>
+      </c>
+      <c r="U155">
+        <v>169</v>
+      </c>
+      <c r="V155">
+        <v>3.4335640000000001</v>
+      </c>
+      <c r="W155">
+        <v>23.053253999999999</v>
+      </c>
+      <c r="X155">
+        <v>114</v>
+      </c>
+      <c r="Y155">
+        <v>34.175438999999997</v>
+      </c>
+    </row>
+    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>25</v>
+      </c>
+      <c r="B156" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" t="s">
+        <v>238</v>
+      </c>
+      <c r="D156" t="s">
+        <v>28</v>
+      </c>
+      <c r="E156" t="s">
+        <v>29</v>
+      </c>
+      <c r="F156">
+        <v>102</v>
+      </c>
+      <c r="G156" t="s">
+        <v>30</v>
+      </c>
+      <c r="H156">
+        <v>3211</v>
+      </c>
+      <c r="I156">
+        <v>1.2276549999999999</v>
+      </c>
+      <c r="J156">
+        <v>43.058823529999998</v>
+      </c>
+      <c r="K156" t="s">
+        <v>42</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>4392</v>
+      </c>
+      <c r="N156" t="s">
+        <v>237</v>
+      </c>
+      <c r="O156">
+        <v>3942</v>
+      </c>
+      <c r="P156">
+        <v>1114.1552509999999</v>
+      </c>
+      <c r="Q156">
+        <v>102</v>
+      </c>
+      <c r="S156">
+        <v>43.058824000000001</v>
+      </c>
+      <c r="T156">
+        <v>2.5875189999999999</v>
+      </c>
+      <c r="U156">
+        <v>116</v>
+      </c>
+      <c r="V156">
+        <v>2.942669</v>
+      </c>
+      <c r="W156">
+        <v>37.862068999999998</v>
+      </c>
+      <c r="X156">
+        <v>80</v>
+      </c>
+      <c r="Y156">
+        <v>54.9</v>
+      </c>
+    </row>
+    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A157" t="s">
+        <v>25</v>
+      </c>
+      <c r="B157" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" t="s">
+        <v>236</v>
+      </c>
+      <c r="D157" t="s">
+        <v>28</v>
+      </c>
+      <c r="E157" t="s">
+        <v>29</v>
+      </c>
+      <c r="F157">
+        <v>81</v>
+      </c>
+      <c r="G157" t="s">
+        <v>41</v>
+      </c>
+      <c r="H157">
+        <v>3360</v>
+      </c>
+      <c r="I157">
+        <v>1.2931550000000001</v>
+      </c>
+      <c r="J157">
+        <v>56.185185189999999</v>
+      </c>
+      <c r="K157" t="s">
+        <v>42</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>4551</v>
+      </c>
+      <c r="N157" t="s">
+        <v>235</v>
+      </c>
+      <c r="O157">
+        <v>4345</v>
+      </c>
+      <c r="P157">
+        <v>1047.410817</v>
+      </c>
+      <c r="Q157">
+        <v>114</v>
+      </c>
+      <c r="S157">
+        <v>39.921053000000001</v>
+      </c>
+      <c r="T157">
+        <v>2.6237050000000002</v>
+      </c>
+      <c r="U157">
+        <v>130</v>
+      </c>
+      <c r="V157">
+        <v>2.9919449999999999</v>
+      </c>
+      <c r="W157">
+        <v>35.007691999999999</v>
+      </c>
+      <c r="X157">
+        <v>81</v>
+      </c>
+      <c r="Y157">
+        <v>56.185184999999997</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A158" t="s">
+        <v>25</v>
+      </c>
+      <c r="B158" t="s">
+        <v>26</v>
+      </c>
+      <c r="C158" t="s">
+        <v>234</v>
+      </c>
+      <c r="D158" t="s">
+        <v>28</v>
+      </c>
+      <c r="E158" t="s">
+        <v>29</v>
+      </c>
+      <c r="F158">
+        <v>109</v>
+      </c>
+      <c r="G158" t="s">
+        <v>41</v>
+      </c>
+      <c r="H158">
+        <v>2904</v>
+      </c>
+      <c r="I158">
+        <v>1.2386360000000001</v>
+      </c>
+      <c r="J158">
+        <v>42.678899080000001</v>
+      </c>
+      <c r="K158" t="s">
+        <v>42</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>4652</v>
+      </c>
+      <c r="N158" t="s">
+        <v>58</v>
+      </c>
+      <c r="O158">
+        <v>3597</v>
+      </c>
+      <c r="P158">
+        <v>1293.299972</v>
+      </c>
+      <c r="Q158">
+        <v>121</v>
+      </c>
+      <c r="S158">
+        <v>38.446280999999999</v>
+      </c>
+      <c r="T158">
+        <v>3.3639139999999998</v>
+      </c>
+      <c r="U158">
+        <v>133</v>
+      </c>
+      <c r="V158">
+        <v>3.6975259999999999</v>
+      </c>
+      <c r="W158">
+        <v>34.977443999999998</v>
+      </c>
+      <c r="X158">
+        <v>109</v>
+      </c>
+      <c r="Y158">
+        <v>42.678899000000001</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A159" t="s">
+        <v>25</v>
+      </c>
+      <c r="B159" t="s">
+        <v>26</v>
+      </c>
+      <c r="C159" t="s">
+        <v>233</v>
+      </c>
+      <c r="D159" t="s">
+        <v>226</v>
+      </c>
+      <c r="E159" t="s">
+        <v>29</v>
+      </c>
+      <c r="F159">
+        <v>40</v>
+      </c>
+      <c r="G159" t="s">
+        <v>41</v>
+      </c>
+      <c r="H159">
+        <v>727</v>
+      </c>
+      <c r="I159">
+        <v>1.037139</v>
+      </c>
+      <c r="J159">
+        <v>36.174999999999997</v>
+      </c>
+      <c r="K159" t="s">
+        <v>42</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>1447</v>
+      </c>
+      <c r="N159" t="s">
+        <v>218</v>
+      </c>
+      <c r="O159">
+        <v>754</v>
+      </c>
+      <c r="P159">
+        <v>1919.0981429999999</v>
+      </c>
+      <c r="Q159">
+        <v>44</v>
+      </c>
+      <c r="S159">
+        <v>32.886364</v>
+      </c>
+      <c r="T159">
+        <v>5.8355439999999996</v>
+      </c>
+      <c r="U159">
+        <v>51</v>
+      </c>
+      <c r="V159">
+        <v>6.7639259999999997</v>
+      </c>
+      <c r="W159">
+        <v>28.372548999999999</v>
+      </c>
+      <c r="X159">
+        <v>40</v>
+      </c>
+      <c r="Y159">
+        <v>36.174999999999997</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A160" t="s">
+        <v>25</v>
+      </c>
+      <c r="B160" t="s">
+        <v>26</v>
+      </c>
+      <c r="C160" t="s">
+        <v>232</v>
+      </c>
+      <c r="D160" t="s">
+        <v>28</v>
+      </c>
+      <c r="E160" t="s">
+        <v>29</v>
+      </c>
+      <c r="F160">
+        <v>27</v>
+      </c>
+      <c r="G160" t="s">
+        <v>41</v>
+      </c>
+      <c r="H160">
+        <v>3975</v>
+      </c>
+      <c r="I160">
+        <v>1.503145</v>
+      </c>
+      <c r="J160">
+        <v>171.55555555999999</v>
+      </c>
+      <c r="K160" t="s">
+        <v>42</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>4632</v>
+      </c>
+      <c r="N160" t="s">
+        <v>52</v>
+      </c>
+      <c r="O160">
+        <v>5975</v>
+      </c>
+      <c r="P160">
+        <v>775.23012600000004</v>
+      </c>
+      <c r="Q160">
+        <v>54</v>
+      </c>
+      <c r="S160">
+        <v>85.777777999999998</v>
+      </c>
+      <c r="T160">
+        <v>0.90376599999999996</v>
+      </c>
+      <c r="U160">
+        <v>63</v>
+      </c>
+      <c r="V160">
+        <v>1.0543929999999999</v>
+      </c>
+      <c r="W160">
+        <v>73.523809999999997</v>
+      </c>
+      <c r="X160">
+        <v>27</v>
+      </c>
+      <c r="Y160">
+        <v>171.555556</v>
+      </c>
+    </row>
+    <row r="161" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A161" t="s">
+        <v>25</v>
+      </c>
+      <c r="B161" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" t="s">
+        <v>231</v>
+      </c>
+      <c r="D161" t="s">
+        <v>28</v>
+      </c>
+      <c r="E161" t="s">
+        <v>29</v>
+      </c>
+      <c r="F161">
+        <v>429</v>
+      </c>
+      <c r="G161" t="s">
+        <v>41</v>
+      </c>
+      <c r="H161">
+        <v>8474</v>
+      </c>
+      <c r="I161">
+        <v>1.5371729999999999</v>
+      </c>
+      <c r="J161">
+        <v>50.216783220000003</v>
+      </c>
+      <c r="K161" t="s">
+        <v>42</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>21543</v>
+      </c>
+      <c r="N161" t="s">
+        <v>230</v>
+      </c>
+      <c r="O161">
+        <v>13026</v>
+      </c>
+      <c r="P161">
+        <v>1653.8461540000001</v>
+      </c>
+      <c r="Q161">
+        <v>489</v>
+      </c>
+      <c r="S161">
+        <v>44.055214999999997</v>
+      </c>
+      <c r="T161">
+        <v>3.7540300000000002</v>
+      </c>
+      <c r="U161">
+        <v>568</v>
+      </c>
+      <c r="V161">
+        <v>4.3605099999999997</v>
+      </c>
+      <c r="W161">
+        <v>37.927816999999997</v>
+      </c>
+      <c r="X161">
+        <v>429</v>
+      </c>
+      <c r="Y161">
+        <v>50.216783</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A162" t="s">
+        <v>25</v>
+      </c>
+      <c r="B162" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" t="s">
+        <v>229</v>
+      </c>
+      <c r="D162" t="s">
+        <v>28</v>
+      </c>
+      <c r="E162" t="s">
+        <v>29</v>
+      </c>
+      <c r="F162">
+        <v>59</v>
+      </c>
+      <c r="G162" t="s">
+        <v>41</v>
+      </c>
+      <c r="H162">
+        <v>3669</v>
+      </c>
+      <c r="I162">
+        <v>1.218043</v>
+      </c>
+      <c r="J162">
+        <v>79.084745760000004</v>
+      </c>
+      <c r="K162" t="s">
+        <v>42</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>4666</v>
+      </c>
+      <c r="N162" t="s">
+        <v>60</v>
+      </c>
+      <c r="O162">
+        <v>4469</v>
+      </c>
+      <c r="P162">
+        <v>1044.0814499999999</v>
+      </c>
+      <c r="Q162">
+        <v>106</v>
+      </c>
+      <c r="S162">
+        <v>44.018867999999998</v>
+      </c>
+      <c r="T162">
+        <v>2.3718949999999999</v>
+      </c>
+      <c r="U162">
+        <v>119</v>
+      </c>
+      <c r="V162">
+        <v>2.6627879999999999</v>
+      </c>
+      <c r="W162">
+        <v>39.210084000000002</v>
+      </c>
+      <c r="X162">
+        <v>59</v>
+      </c>
+      <c r="Y162">
+        <v>79.084745999999996</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A163" t="s">
+        <v>25</v>
+      </c>
+      <c r="B163" t="s">
+        <v>26</v>
+      </c>
+      <c r="C163" t="s">
+        <v>228</v>
+      </c>
+      <c r="D163" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" t="s">
+        <v>29</v>
+      </c>
+      <c r="F163">
+        <v>100</v>
+      </c>
+      <c r="G163" t="s">
+        <v>41</v>
+      </c>
+      <c r="H163">
+        <v>4368</v>
+      </c>
+      <c r="I163">
+        <v>1.32761</v>
+      </c>
+      <c r="J163">
+        <v>50.6</v>
+      </c>
+      <c r="K163" t="s">
+        <v>42</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>5060</v>
+      </c>
+      <c r="N163" t="s">
+        <v>60</v>
+      </c>
+      <c r="O163">
+        <v>5799</v>
+      </c>
+      <c r="P163">
+        <v>872.56423500000005</v>
+      </c>
+      <c r="Q163">
+        <v>114</v>
+      </c>
+      <c r="S163">
+        <v>44.385964999999999</v>
+      </c>
+      <c r="T163">
+        <v>1.965856</v>
+      </c>
+      <c r="U163">
+        <v>132</v>
+      </c>
+      <c r="V163">
+        <v>2.2762549999999999</v>
+      </c>
+      <c r="W163">
+        <v>38.333333000000003</v>
+      </c>
+      <c r="X163">
+        <v>100</v>
+      </c>
+      <c r="Y163">
+        <v>50.6</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A164" t="s">
+        <v>25</v>
+      </c>
+      <c r="B164" t="s">
+        <v>26</v>
+      </c>
+      <c r="C164" t="s">
+        <v>227</v>
+      </c>
+      <c r="D164" t="s">
+        <v>226</v>
+      </c>
+      <c r="E164" t="s">
+        <v>29</v>
+      </c>
+      <c r="H164">
+        <v>216</v>
+      </c>
+      <c r="I164">
+        <v>1.018519</v>
+      </c>
+      <c r="K164" t="s">
+        <v>42</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>260</v>
+      </c>
+      <c r="N164" t="s">
+        <v>215</v>
+      </c>
+      <c r="O164">
+        <v>220</v>
+      </c>
+      <c r="P164">
+        <v>1181.818182</v>
+      </c>
+      <c r="Q164">
+        <v>1</v>
+      </c>
+      <c r="S164">
+        <v>260</v>
+      </c>
+      <c r="T164">
+        <v>0.45454499999999998</v>
+      </c>
+      <c r="U164">
+        <v>2</v>
+      </c>
+      <c r="V164">
+        <v>0.90909099999999998</v>
+      </c>
+      <c r="W164">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A165" t="s">
+        <v>25</v>
+      </c>
+      <c r="B165" t="s">
+        <v>26</v>
+      </c>
+      <c r="C165" t="s">
+        <v>225</v>
+      </c>
+      <c r="D165" t="s">
+        <v>28</v>
+      </c>
+      <c r="E165" t="s">
+        <v>29</v>
+      </c>
+      <c r="F165">
+        <v>43</v>
+      </c>
+      <c r="G165" t="s">
+        <v>41</v>
+      </c>
+      <c r="H165">
+        <v>4704</v>
+      </c>
+      <c r="I165">
+        <v>1.4011480000000001</v>
+      </c>
+      <c r="J165">
+        <v>130.93023256000001</v>
+      </c>
+      <c r="K165" t="s">
+        <v>42</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>5630</v>
+      </c>
+      <c r="N165" t="s">
+        <v>68</v>
+      </c>
+      <c r="O165">
+        <v>6591</v>
+      </c>
+      <c r="P165">
+        <v>854.19511499999999</v>
+      </c>
+      <c r="Q165">
+        <v>75</v>
+      </c>
+      <c r="S165">
+        <v>75.066666999999995</v>
+      </c>
+      <c r="T165">
+        <v>1.137915</v>
+      </c>
+      <c r="U165">
+        <v>85</v>
+      </c>
+      <c r="V165">
+        <v>1.2896369999999999</v>
+      </c>
+      <c r="W165">
+        <v>66.235293999999996</v>
+      </c>
+      <c r="X165">
+        <v>43</v>
+      </c>
+      <c r="Y165">
+        <v>130.93023299999999</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A166" t="s">
+        <v>25</v>
+      </c>
+      <c r="B166" t="s">
+        <v>26</v>
+      </c>
+      <c r="C166" t="s">
+        <v>224</v>
+      </c>
+      <c r="D166" t="s">
+        <v>28</v>
+      </c>
+      <c r="E166" t="s">
+        <v>29</v>
+      </c>
+      <c r="F166">
+        <v>179</v>
+      </c>
+      <c r="G166" t="s">
+        <v>41</v>
+      </c>
+      <c r="H166">
+        <v>4046</v>
+      </c>
+      <c r="I166">
+        <v>1.542511</v>
+      </c>
+      <c r="J166">
+        <v>30.787709499999998</v>
+      </c>
+      <c r="K166" t="s">
+        <v>42</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>5511</v>
+      </c>
+      <c r="N166" t="s">
+        <v>68</v>
+      </c>
+      <c r="O166">
+        <v>6241</v>
+      </c>
+      <c r="P166">
+        <v>883.031565</v>
+      </c>
+      <c r="Q166">
+        <v>202</v>
+      </c>
+      <c r="S166">
+        <v>27.282177999999998</v>
+      </c>
+      <c r="T166">
+        <v>3.2366609999999998</v>
+      </c>
+      <c r="U166">
+        <v>257</v>
+      </c>
+      <c r="V166">
+        <v>4.1179300000000003</v>
+      </c>
+      <c r="W166">
+        <v>21.443580000000001</v>
+      </c>
+      <c r="X166">
+        <v>179</v>
+      </c>
+      <c r="Y166">
+        <v>30.787710000000001</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A167" t="s">
+        <v>25</v>
+      </c>
+      <c r="B167" t="s">
+        <v>26</v>
+      </c>
+      <c r="C167" t="s">
+        <v>223</v>
+      </c>
+      <c r="D167" t="s">
+        <v>108</v>
+      </c>
+      <c r="E167" t="s">
+        <v>29</v>
+      </c>
+      <c r="F167">
+        <v>24</v>
+      </c>
+      <c r="G167" t="s">
+        <v>41</v>
+      </c>
+      <c r="H167">
+        <v>1512</v>
+      </c>
+      <c r="I167">
+        <v>1.0932539999999999</v>
+      </c>
+      <c r="J167">
+        <v>68.875</v>
+      </c>
+      <c r="K167" t="s">
+        <v>42</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>1653</v>
+      </c>
+      <c r="N167" t="s">
+        <v>72</v>
+      </c>
+      <c r="O167">
+        <v>1653</v>
+      </c>
+      <c r="P167">
+        <v>1000</v>
+      </c>
+      <c r="Q167">
+        <v>29</v>
+      </c>
+      <c r="S167">
+        <v>57</v>
+      </c>
+      <c r="T167">
+        <v>1.754386</v>
+      </c>
+      <c r="U167">
+        <v>44</v>
+      </c>
+      <c r="V167">
+        <v>2.6618270000000002</v>
+      </c>
+      <c r="W167">
+        <v>37.568182</v>
+      </c>
+      <c r="X167">
+        <v>24</v>
+      </c>
+      <c r="Y167">
+        <v>68.875</v>
+      </c>
+    </row>
+    <row r="168" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A168" t="s">
+        <v>25</v>
+      </c>
+      <c r="B168" t="s">
+        <v>26</v>
+      </c>
+      <c r="C168" t="s">
+        <v>222</v>
+      </c>
+      <c r="D168" t="s">
+        <v>28</v>
+      </c>
+      <c r="E168" t="s">
+        <v>29</v>
+      </c>
+      <c r="F168">
+        <v>65</v>
+      </c>
+      <c r="G168" t="s">
+        <v>41</v>
+      </c>
+      <c r="H168">
+        <v>3927</v>
+      </c>
+      <c r="I168">
+        <v>1.2426790000000001</v>
+      </c>
+      <c r="J168">
+        <v>75.38461538</v>
+      </c>
+      <c r="K168" t="s">
+        <v>42</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>4900</v>
+      </c>
+      <c r="N168" t="s">
+        <v>221</v>
+      </c>
+      <c r="O168">
+        <v>4880</v>
+      </c>
+      <c r="P168">
+        <v>1004.098361</v>
+      </c>
+      <c r="Q168">
+        <v>78</v>
+      </c>
+      <c r="S168">
+        <v>62.820512999999998</v>
+      </c>
+      <c r="T168">
+        <v>1.5983609999999999</v>
+      </c>
+      <c r="U168">
+        <v>83</v>
+      </c>
+      <c r="V168">
+        <v>1.70082</v>
+      </c>
+      <c r="W168">
+        <v>59.036144999999998</v>
+      </c>
+      <c r="X168">
+        <v>65</v>
+      </c>
+      <c r="Y168">
+        <v>75.384614999999997</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A169" t="s">
+        <v>25</v>
+      </c>
+      <c r="B169" t="s">
+        <v>26</v>
+      </c>
+      <c r="C169" t="s">
+        <v>220</v>
+      </c>
+      <c r="D169" t="s">
+        <v>108</v>
+      </c>
+      <c r="E169" t="s">
+        <v>29</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="K169" t="s">
+        <v>42</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169" t="s">
+        <v>218</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+      <c r="U169">
+        <v>0</v>
+      </c>
+      <c r="V169">
+        <v>0</v>
+      </c>
+      <c r="W169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A170" t="s">
+        <v>25</v>
+      </c>
+      <c r="B170" t="s">
+        <v>26</v>
+      </c>
+      <c r="C170" t="s">
+        <v>219</v>
+      </c>
+      <c r="D170" t="s">
+        <v>108</v>
+      </c>
+      <c r="E170" t="s">
+        <v>29</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="K170" t="s">
+        <v>42</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170" t="s">
+        <v>218</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>0</v>
+      </c>
+      <c r="U170">
+        <v>0</v>
+      </c>
+      <c r="V170">
+        <v>0</v>
+      </c>
+      <c r="W170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A171" t="s">
+        <v>25</v>
+      </c>
+      <c r="B171" t="s">
+        <v>26</v>
+      </c>
+      <c r="C171" t="s">
+        <v>82</v>
+      </c>
+      <c r="D171" t="s">
+        <v>108</v>
+      </c>
+      <c r="E171" t="s">
+        <v>29</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="K171" t="s">
+        <v>42</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171" t="s">
+        <v>217</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+      <c r="U171">
+        <v>0</v>
+      </c>
+      <c r="V171">
+        <v>0</v>
+      </c>
+      <c r="W171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="A172" t="s">
+        <v>25</v>
+      </c>
+      <c r="B172" t="s">
+        <v>26</v>
+      </c>
+      <c r="C172" t="s">
+        <v>216</v>
+      </c>
+      <c r="D172" t="s">
+        <v>108</v>
+      </c>
+      <c r="E172" t="s">
+        <v>29</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="K172" t="s">
+        <v>42</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172" t="s">
+        <v>215</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+      <c r="U172">
+        <v>0</v>
+      </c>
+      <c r="V172">
+        <v>0</v>
+      </c>
+      <c r="W172">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
